--- a/docs/3-编队算法设计文档/集中式通信+长机僚机+PID控制+三角队形+1个航段.xlsx
+++ b/docs/3-编队算法设计文档/集中式通信+长机僚机+PID控制+三角队形+1个航段.xlsx
@@ -2,137 +2,54 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitHub\Simu\simu-cc\docs\3-编队算法设计文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02539B07-8D00-4F2A-BD39-7DC5319359E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC99E4E-D1D3-4093-9799-AA04DFF6EC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2970" windowWidth="29040" windowHeight="15720" xr2:uid="{BFCF63F1-0F58-420E-B817-D43F2F82AE0D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="38">
-  <si>
-    <t>任务编排</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+  <si>
+    <t>共有信息（网络拓扑、队形信息（各个飞机id的位置信息））</t>
+  </si>
+  <si>
+    <t>长机（独有稳定信息：飞机id）</t>
+  </si>
+  <si>
+    <t>僚机（独有稳定信息：飞机ID）</t>
+  </si>
+  <si>
+    <t>动作</t>
   </si>
   <si>
     <t>u</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>轨迹规划</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>位置解算</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>误差解算</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>跟踪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>发送消息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>动作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>收消息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>管理当前的飞行模态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>解算需要跟踪的航段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计算制导误差</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>三轴加速度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>编队跟踪算法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>接受并解析需要的数据</t>
   </si>
   <si>
     <t>list[MessageEnvelope]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>接受并解析需要的数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>基于航段计算位置指令</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标指令{东北高+航迹偏航角+航迹倾角+速度}
-本体运动状态{东北高+航迹偏航角+速度+航迹倾角}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>共有信息（网络拓扑、队形信息（各个飞机id的位置信息））</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>僚机（独有稳定信息：飞机ID）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>长机（独有稳定信息：飞机id）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>三轴位置误差和速度误差</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>长机运动状态{东北高+航迹偏航角+速度+航迹倾角}
@@ -140,6 +57,12 @@
 队形指令</t>
   </si>
   <si>
+    <t>任务编排</t>
+  </si>
+  <si>
+    <t>管理当前的飞行模态</t>
+  </si>
+  <si>
     <t>遥控指令
 上一拍的编队模式{集结、保持、重构}</t>
   </si>
@@ -148,118 +71,82 @@
 队形指令</t>
   </si>
   <si>
+    <t>轨迹规划</t>
+  </si>
+  <si>
+    <t>解算需要跟踪的航段</t>
+  </si>
+  <si>
+    <t>编队模式{集结、保持、重构}
+上一拍航段信息{航段号、起始东北高、终点东北高、速度指令}
+本体运动状态{东北高+航迹偏航角+速度+航迹倾角}</t>
+  </si>
+  <si>
     <t>航段信息{航段号、起始东北高、终点东北高、速度指令}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本次目标：1个航段+集中式通信+长机僚机+PID控制+三角队形</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>轨迹规划(本场景这一步没有任何意义，但是
+为了兼容后续集结流程，因此先预埋)</t>
+  </si>
+  <si>
+    <t>位置解算</t>
+  </si>
+  <si>
+    <t>基于航段计算位置指令</t>
+  </si>
+  <si>
+    <t>航段信息{航段号、起始东北高、终点东北高、速度指令}
+本体运动状态{东北高+航迹偏航角+速度+航迹倾角}
+队形指令（长机其实不需要，为了拉齐这里补充）
+主机运动状态{东北高+航迹偏航角+速度+航迹倾角}</t>
+  </si>
+  <si>
+    <t>目标指令{东北高+航迹偏航角+航迹倾角+速度}</t>
   </si>
   <si>
     <t>基于主机位置+队形+槽位号计算位置指令
 init(飞机ID、队形信息)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>发送信息
-init(网络拓扑)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>三轴位置误差和速度误差</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(此时前向的位置误差为0)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>队形指令
-主机运动状态{东北高+航迹偏航角+速度+航迹倾角}
-编队模式{集结、保持、重构}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>轨迹规划</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(本场景这一步没有任何意义，但是
-为了兼容后续集结流程，因此先预埋)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>航段信息{航段号、起始东北高、终点东北高、速度指令}
 本体运动状态{东北高+航迹偏航角+速度+航迹倾角}
 队形指令
 主机运动状态{东北高+航迹偏航角+速度+航迹倾角}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>航段信息{航段号、起始东北高、终点东北高、速度指令}
-本体运动状态{东北高+航迹偏航角+速度+航迹倾角}
-队形指令</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（长机其实不需要，为了拉齐这里补充）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-主机运动状态{东北高+航迹偏航角+速度+航迹倾角}</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>编队模式{集结、保持、重构}
-上一拍航段信息{航段号、起始东北高、终点东北高、速度指令}
+  </si>
+  <si>
+    <t>跟踪</t>
+  </si>
+  <si>
+    <t>编队跟踪算法（含求偏差）</t>
+  </si>
+  <si>
+    <t>目标指令{东北高+航迹偏航角+航迹倾角+速度}
 本体运动状态{东北高+航迹偏航角+速度+航迹倾角}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标指令{东北高+航迹偏航角+航迹倾角+速度}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三轴加速度</t>
+  </si>
+  <si>
+    <t>发送消息</t>
+  </si>
+  <si>
+    <t>发送信息
+init(网络拓扑)</t>
+  </si>
+  <si>
+    <t>队形指令
+主机运动状态{东北高+航迹偏航角+速度+航迹倾角}
+编队模式{集结、保持、重构}</t>
+  </si>
+  <si>
+    <t>本次目标：1个航段+集中式通信+长机僚机+PID控制+三角队形</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,22 +166,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -360,36 +231,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -504,19 +345,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -540,106 +368,136 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="32">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -973,22 +831,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FAECD76-16D6-4BA3-9F06-679A5096AEEB}">
-  <dimension ref="B1:H13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:H11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="23.75" customWidth="1"/>
-    <col min="4" max="4" width="59.125" customWidth="1"/>
-    <col min="5" max="5" width="51.75" customWidth="1"/>
-    <col min="6" max="6" width="36.875" customWidth="1"/>
-    <col min="7" max="7" width="49" customWidth="1"/>
-    <col min="8" max="8" width="70.625" customWidth="1"/>
+    <col min="3" max="3" width="23.75" style="23" customWidth="1"/>
+    <col min="4" max="4" width="59.125" style="23" customWidth="1"/>
+    <col min="5" max="5" width="51.75" style="23" customWidth="1"/>
+    <col min="6" max="6" width="36.875" style="23" customWidth="1"/>
+    <col min="7" max="7" width="49" style="23" customWidth="1"/>
+    <col min="8" max="8" width="70.625" style="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="26" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C2" s="27"/>
       <c r="D2" s="27"/>
@@ -999,204 +857,181 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B3" s="11"/>
-      <c r="C3" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="24"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="24"/>
-      <c r="H3" s="25"/>
+      <c r="C3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="30"/>
+      <c r="H3" s="31"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B4" s="12"/>
       <c r="C4" s="8" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="13" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="6"/>
       <c r="F5" s="2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="6"/>
     </row>
     <row r="7" spans="2:8" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="13" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="13" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>23</v>
-      </c>
+      <c r="D10" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="20"/>
     </row>
-    <row r="10" spans="2:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="19"/>
-      <c r="H11" s="20"/>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B13" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B11" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B2:H2"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="F3:H3"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B13:H13"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
